--- a/build/Twin_Visit_Logger_DEV_reference.xlsx
+++ b/build/Twin_Visit_Logger_DEV_reference.xlsx
@@ -6573,8 +6573,8 @@
     <dataValidation sqref="AV2:AV1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a value from the list." prompt="Allowed: Not Ready,Ready for Handoff,Handed Off to JM,JM Confirmed" type="list">
       <formula1>"Not Ready,Ready for Handoff,Handed Off to JM,JM Confirmed"</formula1>
     </dataValidation>
-    <dataValidation sqref="BB2:BB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a value from the list." prompt="Allowed: Jonathan,Kyle,Cherry,Juan,JM,Apps Script" type="list">
-      <formula1>"Jonathan,Kyle,Cherry,Juan,JM,Apps Script"</formula1>
+    <dataValidation sqref="BB2:BB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a value from the list." prompt="Allowed: Jonathan,Kyle,Cherry,Juan,JM,Apps Script,Import" type="list">
+      <formula1>"Jonathan,Kyle,Cherry,Juan,JM,Apps Script,Import"</formula1>
     </dataValidation>
     <dataValidation sqref="BC2:BC1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a value from the list." prompt="Allowed: Manual,Apps Script,Import,TEST" type="list">
       <formula1>"Manual,Apps Script,Import,TEST"</formula1>
@@ -7197,6 +7197,11 @@
           <t>Jose Herrera</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Import</t>
+        </is>
+      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>Documents</t>

--- a/build/Twin_Visit_Logger_DEV_reference.xlsx
+++ b/build/Twin_Visit_Logger_DEV_reference.xlsx
@@ -1550,7 +1550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG60"/>
+  <dimension ref="A1:BI60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1612,6 +1612,8 @@
     <col width="34" customWidth="1" min="57" max="57"/>
     <col width="16" customWidth="1" min="58" max="58"/>
     <col width="16" customWidth="1" min="59" max="59"/>
+    <col width="16" customWidth="1" min="60" max="60"/>
+    <col width="16" customWidth="1" min="61" max="61"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -1908,6 +1910,16 @@
       <c r="BG1" s="18" t="inlineStr">
         <is>
           <t>REI Update Completed</t>
+        </is>
+      </c>
+      <c r="BH1" s="15" t="inlineStr">
+        <is>
+          <t>Gift Approved By</t>
+        </is>
+      </c>
+      <c r="BI1" s="15" t="inlineStr">
+        <is>
+          <t>Gift Approval Date</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2065,7 @@
         <v/>
       </c>
       <c r="BE2" s="19">
-        <f>IF($B2="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K2="Completed",$M2=""),"Completed visit missing Visit Notes",""),IF(AND($K2="Completed",$S2=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ2="Offer Sent",OR($X2="",$AA2="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ2="Active Negotiation",OR($AE2="",$AF2="",$AH2="",$AG2="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ2="Contract Sent",$AT2="",$R2=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ2="Contract Signed",$AU2=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ2="Long-Term Nurture",OR($AG2="",$AG2&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ2="Lost / Closed Out",OR($AR2="",$AS2="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM2="Sent",$AO2=""),"Gift marked Sent without recorded approval",""),IF($AX2="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B2="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K2="Completed",$M2=""),"Completed visit missing Visit Notes",""),IF(AND($K2="Completed",$S2=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ2="Offer Sent",OR($X2="",$AA2="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ2="Active Negotiation",OR($AE2="",$AF2="",$AH2="",$AG2="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ2="Contract Sent",$AT2="",$R2=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ2="Contract Signed",$AU2=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ2="Long-Term Nurture",OR($AG2="",$AG2&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ2="Lost / Closed Out",OR($AR2="",$AS2="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM2="Sent",OR($BH2="",$BI2="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX2="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF2" s="19" t="inlineStr">
@@ -2062,6 +2074,8 @@
         </is>
       </c>
       <c r="BG2" s="19" t="n"/>
+      <c r="BH2" s="19" t="n"/>
+      <c r="BI2" s="19" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="19" t="inlineStr">
@@ -2205,7 +2219,7 @@
         <v/>
       </c>
       <c r="BE3" s="19">
-        <f>IF($B3="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K3="Completed",$M3=""),"Completed visit missing Visit Notes",""),IF(AND($K3="Completed",$S3=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ3="Offer Sent",OR($X3="",$AA3="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ3="Active Negotiation",OR($AE3="",$AF3="",$AH3="",$AG3="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ3="Contract Sent",$AT3="",$R3=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ3="Contract Signed",$AU3=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ3="Long-Term Nurture",OR($AG3="",$AG3&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ3="Lost / Closed Out",OR($AR3="",$AS3="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM3="Sent",$AO3=""),"Gift marked Sent without recorded approval",""),IF($AX3="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B3="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K3="Completed",$M3=""),"Completed visit missing Visit Notes",""),IF(AND($K3="Completed",$S3=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ3="Offer Sent",OR($X3="",$AA3="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ3="Active Negotiation",OR($AE3="",$AF3="",$AH3="",$AG3="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ3="Contract Sent",$AT3="",$R3=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ3="Contract Signed",$AU3=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ3="Long-Term Nurture",OR($AG3="",$AG3&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ3="Lost / Closed Out",OR($AR3="",$AS3="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM3="Sent",OR($BH3="",$BI3="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX3="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF3" s="19" t="inlineStr">
@@ -2214,6 +2228,8 @@
         </is>
       </c>
       <c r="BG3" s="19" t="n"/>
+      <c r="BH3" s="19" t="n"/>
+      <c r="BI3" s="19" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="19" t="inlineStr">
@@ -2371,7 +2387,7 @@
         <v/>
       </c>
       <c r="BE4" s="19">
-        <f>IF($B4="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K4="Completed",$M4=""),"Completed visit missing Visit Notes",""),IF(AND($K4="Completed",$S4=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ4="Offer Sent",OR($X4="",$AA4="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ4="Active Negotiation",OR($AE4="",$AF4="",$AH4="",$AG4="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ4="Contract Sent",$AT4="",$R4=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ4="Contract Signed",$AU4=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ4="Long-Term Nurture",OR($AG4="",$AG4&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ4="Lost / Closed Out",OR($AR4="",$AS4="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM4="Sent",$AO4=""),"Gift marked Sent without recorded approval",""),IF($AX4="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B4="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K4="Completed",$M4=""),"Completed visit missing Visit Notes",""),IF(AND($K4="Completed",$S4=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ4="Offer Sent",OR($X4="",$AA4="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ4="Active Negotiation",OR($AE4="",$AF4="",$AH4="",$AG4="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ4="Contract Sent",$AT4="",$R4=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ4="Contract Signed",$AU4=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ4="Long-Term Nurture",OR($AG4="",$AG4&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ4="Lost / Closed Out",OR($AR4="",$AS4="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM4="Sent",OR($BH4="",$BI4="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX4="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF4" s="19" t="inlineStr">
@@ -2380,6 +2396,8 @@
         </is>
       </c>
       <c r="BG4" s="19" t="n"/>
+      <c r="BH4" s="19" t="n"/>
+      <c r="BI4" s="19" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
@@ -2517,11 +2535,13 @@
         <v/>
       </c>
       <c r="BE5" s="19">
-        <f>IF($B5="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K5="Completed",$M5=""),"Completed visit missing Visit Notes",""),IF(AND($K5="Completed",$S5=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ5="Offer Sent",OR($X5="",$AA5="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ5="Active Negotiation",OR($AE5="",$AF5="",$AH5="",$AG5="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ5="Contract Sent",$AT5="",$R5=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ5="Contract Signed",$AU5=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ5="Long-Term Nurture",OR($AG5="",$AG5&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ5="Lost / Closed Out",OR($AR5="",$AS5="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM5="Sent",$AO5=""),"Gift marked Sent without recorded approval",""),IF($AX5="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B5="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K5="Completed",$M5=""),"Completed visit missing Visit Notes",""),IF(AND($K5="Completed",$S5=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ5="Offer Sent",OR($X5="",$AA5="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ5="Active Negotiation",OR($AE5="",$AF5="",$AH5="",$AG5="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ5="Contract Sent",$AT5="",$R5=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ5="Contract Signed",$AU5=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ5="Long-Term Nurture",OR($AG5="",$AG5&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ5="Lost / Closed Out",OR($AR5="",$AS5="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM5="Sent",OR($BH5="",$BI5="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX5="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF5" s="19" t="n"/>
       <c r="BG5" s="19" t="n"/>
+      <c r="BH5" s="19" t="n"/>
+      <c r="BI5" s="19" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
@@ -2663,11 +2683,13 @@
         <v/>
       </c>
       <c r="BE6" s="19">
-        <f>IF($B6="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K6="Completed",$M6=""),"Completed visit missing Visit Notes",""),IF(AND($K6="Completed",$S6=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ6="Offer Sent",OR($X6="",$AA6="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ6="Active Negotiation",OR($AE6="",$AF6="",$AH6="",$AG6="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ6="Contract Sent",$AT6="",$R6=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ6="Contract Signed",$AU6=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ6="Long-Term Nurture",OR($AG6="",$AG6&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ6="Lost / Closed Out",OR($AR6="",$AS6="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM6="Sent",$AO6=""),"Gift marked Sent without recorded approval",""),IF($AX6="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B6="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K6="Completed",$M6=""),"Completed visit missing Visit Notes",""),IF(AND($K6="Completed",$S6=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ6="Offer Sent",OR($X6="",$AA6="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ6="Active Negotiation",OR($AE6="",$AF6="",$AH6="",$AG6="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ6="Contract Sent",$AT6="",$R6=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ6="Contract Signed",$AU6=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ6="Long-Term Nurture",OR($AG6="",$AG6&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ6="Lost / Closed Out",OR($AR6="",$AS6="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM6="Sent",OR($BH6="",$BI6="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX6="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF6" s="19" t="n"/>
       <c r="BG6" s="19" t="n"/>
+      <c r="BH6" s="19" t="n"/>
+      <c r="BI6" s="19" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
@@ -2813,11 +2835,13 @@
         <v/>
       </c>
       <c r="BE7" s="19">
-        <f>IF($B7="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K7="Completed",$M7=""),"Completed visit missing Visit Notes",""),IF(AND($K7="Completed",$S7=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ7="Offer Sent",OR($X7="",$AA7="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ7="Active Negotiation",OR($AE7="",$AF7="",$AH7="",$AG7="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ7="Contract Sent",$AT7="",$R7=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ7="Contract Signed",$AU7=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ7="Long-Term Nurture",OR($AG7="",$AG7&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ7="Lost / Closed Out",OR($AR7="",$AS7="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM7="Sent",$AO7=""),"Gift marked Sent without recorded approval",""),IF($AX7="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B7="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K7="Completed",$M7=""),"Completed visit missing Visit Notes",""),IF(AND($K7="Completed",$S7=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ7="Offer Sent",OR($X7="",$AA7="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ7="Active Negotiation",OR($AE7="",$AF7="",$AH7="",$AG7="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ7="Contract Sent",$AT7="",$R7=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ7="Contract Signed",$AU7=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ7="Long-Term Nurture",OR($AG7="",$AG7&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ7="Lost / Closed Out",OR($AR7="",$AS7="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM7="Sent",OR($BH7="",$BI7="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX7="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF7" s="19" t="n"/>
       <c r="BG7" s="19" t="n"/>
+      <c r="BH7" s="19" t="n"/>
+      <c r="BI7" s="19" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
@@ -2967,11 +2991,13 @@
         <v/>
       </c>
       <c r="BE8" s="19">
-        <f>IF($B8="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K8="Completed",$M8=""),"Completed visit missing Visit Notes",""),IF(AND($K8="Completed",$S8=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ8="Offer Sent",OR($X8="",$AA8="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ8="Active Negotiation",OR($AE8="",$AF8="",$AH8="",$AG8="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ8="Contract Sent",$AT8="",$R8=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ8="Contract Signed",$AU8=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ8="Long-Term Nurture",OR($AG8="",$AG8&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ8="Lost / Closed Out",OR($AR8="",$AS8="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM8="Sent",$AO8=""),"Gift marked Sent without recorded approval",""),IF($AX8="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B8="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K8="Completed",$M8=""),"Completed visit missing Visit Notes",""),IF(AND($K8="Completed",$S8=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ8="Offer Sent",OR($X8="",$AA8="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ8="Active Negotiation",OR($AE8="",$AF8="",$AH8="",$AG8="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ8="Contract Sent",$AT8="",$R8=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ8="Contract Signed",$AU8=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ8="Long-Term Nurture",OR($AG8="",$AG8&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ8="Lost / Closed Out",OR($AR8="",$AS8="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM8="Sent",OR($BH8="",$BI8="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX8="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF8" s="19" t="n"/>
       <c r="BG8" s="19" t="n"/>
+      <c r="BH8" s="19" t="n"/>
+      <c r="BI8" s="19" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
@@ -3109,11 +3135,13 @@
         <v/>
       </c>
       <c r="BE9" s="19">
-        <f>IF($B9="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K9="Completed",$M9=""),"Completed visit missing Visit Notes",""),IF(AND($K9="Completed",$S9=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ9="Offer Sent",OR($X9="",$AA9="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ9="Active Negotiation",OR($AE9="",$AF9="",$AH9="",$AG9="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ9="Contract Sent",$AT9="",$R9=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ9="Contract Signed",$AU9=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ9="Long-Term Nurture",OR($AG9="",$AG9&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ9="Lost / Closed Out",OR($AR9="",$AS9="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM9="Sent",$AO9=""),"Gift marked Sent without recorded approval",""),IF($AX9="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B9="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K9="Completed",$M9=""),"Completed visit missing Visit Notes",""),IF(AND($K9="Completed",$S9=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ9="Offer Sent",OR($X9="",$AA9="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ9="Active Negotiation",OR($AE9="",$AF9="",$AH9="",$AG9="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ9="Contract Sent",$AT9="",$R9=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ9="Contract Signed",$AU9=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ9="Long-Term Nurture",OR($AG9="",$AG9&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ9="Lost / Closed Out",OR($AR9="",$AS9="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM9="Sent",OR($BH9="",$BI9="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX9="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF9" s="19" t="n"/>
       <c r="BG9" s="19" t="n"/>
+      <c r="BH9" s="19" t="n"/>
+      <c r="BI9" s="19" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
@@ -3275,7 +3303,7 @@
         <v/>
       </c>
       <c r="BE10" s="19">
-        <f>IF($B10="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K10="Completed",$M10=""),"Completed visit missing Visit Notes",""),IF(AND($K10="Completed",$S10=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ10="Offer Sent",OR($X10="",$AA10="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ10="Active Negotiation",OR($AE10="",$AF10="",$AH10="",$AG10="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ10="Contract Sent",$AT10="",$R10=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ10="Contract Signed",$AU10=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ10="Long-Term Nurture",OR($AG10="",$AG10&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ10="Lost / Closed Out",OR($AR10="",$AS10="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM10="Sent",$AO10=""),"Gift marked Sent without recorded approval",""),IF($AX10="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B10="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K10="Completed",$M10=""),"Completed visit missing Visit Notes",""),IF(AND($K10="Completed",$S10=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ10="Offer Sent",OR($X10="",$AA10="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ10="Active Negotiation",OR($AE10="",$AF10="",$AH10="",$AG10="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ10="Contract Sent",$AT10="",$R10=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ10="Contract Signed",$AU10=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ10="Long-Term Nurture",OR($AG10="",$AG10&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ10="Lost / Closed Out",OR($AR10="",$AS10="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM10="Sent",OR($BH10="",$BI10="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX10="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF10" s="19" t="inlineStr">
@@ -3284,6 +3312,8 @@
         </is>
       </c>
       <c r="BG10" s="19" t="n"/>
+      <c r="BH10" s="19" t="n"/>
+      <c r="BI10" s="19" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
@@ -3433,11 +3463,13 @@
         <v/>
       </c>
       <c r="BE11" s="19">
-        <f>IF($B11="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K11="Completed",$M11=""),"Completed visit missing Visit Notes",""),IF(AND($K11="Completed",$S11=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ11="Offer Sent",OR($X11="",$AA11="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ11="Active Negotiation",OR($AE11="",$AF11="",$AH11="",$AG11="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ11="Contract Sent",$AT11="",$R11=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ11="Contract Signed",$AU11=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ11="Long-Term Nurture",OR($AG11="",$AG11&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ11="Lost / Closed Out",OR($AR11="",$AS11="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM11="Sent",$AO11=""),"Gift marked Sent without recorded approval",""),IF($AX11="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B11="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K11="Completed",$M11=""),"Completed visit missing Visit Notes",""),IF(AND($K11="Completed",$S11=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ11="Offer Sent",OR($X11="",$AA11="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ11="Active Negotiation",OR($AE11="",$AF11="",$AH11="",$AG11="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ11="Contract Sent",$AT11="",$R11=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ11="Contract Signed",$AU11=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ11="Long-Term Nurture",OR($AG11="",$AG11&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ11="Lost / Closed Out",OR($AR11="",$AS11="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM11="Sent",OR($BH11="",$BI11="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX11="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF11" s="19" t="n"/>
       <c r="BG11" s="19" t="n"/>
+      <c r="BH11" s="19" t="n"/>
+      <c r="BI11" s="19" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
@@ -3603,7 +3635,7 @@
         <v/>
       </c>
       <c r="BE12" s="19">
-        <f>IF($B12="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K12="Completed",$M12=""),"Completed visit missing Visit Notes",""),IF(AND($K12="Completed",$S12=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ12="Offer Sent",OR($X12="",$AA12="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ12="Active Negotiation",OR($AE12="",$AF12="",$AH12="",$AG12="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ12="Contract Sent",$AT12="",$R12=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ12="Contract Signed",$AU12=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ12="Long-Term Nurture",OR($AG12="",$AG12&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ12="Lost / Closed Out",OR($AR12="",$AS12="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM12="Sent",$AO12=""),"Gift marked Sent without recorded approval",""),IF($AX12="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B12="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K12="Completed",$M12=""),"Completed visit missing Visit Notes",""),IF(AND($K12="Completed",$S12=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ12="Offer Sent",OR($X12="",$AA12="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ12="Active Negotiation",OR($AE12="",$AF12="",$AH12="",$AG12="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ12="Contract Sent",$AT12="",$R12=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ12="Contract Signed",$AU12=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ12="Long-Term Nurture",OR($AG12="",$AG12&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ12="Lost / Closed Out",OR($AR12="",$AS12="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM12="Sent",OR($BH12="",$BI12="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX12="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF12" s="19" t="inlineStr">
@@ -3612,6 +3644,8 @@
         </is>
       </c>
       <c r="BG12" s="19" t="n"/>
+      <c r="BH12" s="19" t="n"/>
+      <c r="BI12" s="19" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
@@ -3783,7 +3817,7 @@
         <v/>
       </c>
       <c r="BE13" s="19">
-        <f>IF($B13="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K13="Completed",$M13=""),"Completed visit missing Visit Notes",""),IF(AND($K13="Completed",$S13=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ13="Offer Sent",OR($X13="",$AA13="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ13="Active Negotiation",OR($AE13="",$AF13="",$AH13="",$AG13="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ13="Contract Sent",$AT13="",$R13=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ13="Contract Signed",$AU13=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ13="Long-Term Nurture",OR($AG13="",$AG13&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ13="Lost / Closed Out",OR($AR13="",$AS13="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM13="Sent",$AO13=""),"Gift marked Sent without recorded approval",""),IF($AX13="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B13="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K13="Completed",$M13=""),"Completed visit missing Visit Notes",""),IF(AND($K13="Completed",$S13=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ13="Offer Sent",OR($X13="",$AA13="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ13="Active Negotiation",OR($AE13="",$AF13="",$AH13="",$AG13="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ13="Contract Sent",$AT13="",$R13=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ13="Contract Signed",$AU13=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ13="Long-Term Nurture",OR($AG13="",$AG13&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ13="Lost / Closed Out",OR($AR13="",$AS13="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM13="Sent",OR($BH13="",$BI13="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX13="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF13" s="19" t="inlineStr">
@@ -3792,6 +3826,8 @@
         </is>
       </c>
       <c r="BG13" s="19" t="n"/>
+      <c r="BH13" s="19" t="n"/>
+      <c r="BI13" s="19" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
@@ -3969,7 +4005,7 @@
         <v/>
       </c>
       <c r="BE14" s="19">
-        <f>IF($B14="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K14="Completed",$M14=""),"Completed visit missing Visit Notes",""),IF(AND($K14="Completed",$S14=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ14="Offer Sent",OR($X14="",$AA14="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ14="Active Negotiation",OR($AE14="",$AF14="",$AH14="",$AG14="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ14="Contract Sent",$AT14="",$R14=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ14="Contract Signed",$AU14=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ14="Long-Term Nurture",OR($AG14="",$AG14&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ14="Lost / Closed Out",OR($AR14="",$AS14="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM14="Sent",$AO14=""),"Gift marked Sent without recorded approval",""),IF($AX14="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B14="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K14="Completed",$M14=""),"Completed visit missing Visit Notes",""),IF(AND($K14="Completed",$S14=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ14="Offer Sent",OR($X14="",$AA14="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ14="Active Negotiation",OR($AE14="",$AF14="",$AH14="",$AG14="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ14="Contract Sent",$AT14="",$R14=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ14="Contract Signed",$AU14=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ14="Long-Term Nurture",OR($AG14="",$AG14&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ14="Lost / Closed Out",OR($AR14="",$AS14="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM14="Sent",OR($BH14="",$BI14="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX14="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF14" s="19" t="inlineStr">
@@ -3978,6 +4014,8 @@
         </is>
       </c>
       <c r="BG14" s="19" t="n"/>
+      <c r="BH14" s="19" t="n"/>
+      <c r="BI14" s="19" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
@@ -4135,7 +4173,7 @@
         <v/>
       </c>
       <c r="BE15" s="19">
-        <f>IF($B15="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K15="Completed",$M15=""),"Completed visit missing Visit Notes",""),IF(AND($K15="Completed",$S15=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ15="Offer Sent",OR($X15="",$AA15="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ15="Active Negotiation",OR($AE15="",$AF15="",$AH15="",$AG15="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ15="Contract Sent",$AT15="",$R15=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ15="Contract Signed",$AU15=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ15="Long-Term Nurture",OR($AG15="",$AG15&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ15="Lost / Closed Out",OR($AR15="",$AS15="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM15="Sent",$AO15=""),"Gift marked Sent without recorded approval",""),IF($AX15="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B15="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K15="Completed",$M15=""),"Completed visit missing Visit Notes",""),IF(AND($K15="Completed",$S15=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ15="Offer Sent",OR($X15="",$AA15="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ15="Active Negotiation",OR($AE15="",$AF15="",$AH15="",$AG15="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ15="Contract Sent",$AT15="",$R15=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ15="Contract Signed",$AU15=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ15="Long-Term Nurture",OR($AG15="",$AG15&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ15="Lost / Closed Out",OR($AR15="",$AS15="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM15="Sent",OR($BH15="",$BI15="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX15="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF15" s="19" t="inlineStr">
@@ -4144,6 +4182,8 @@
         </is>
       </c>
       <c r="BG15" s="19" t="n"/>
+      <c r="BH15" s="19" t="n"/>
+      <c r="BI15" s="19" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
@@ -4309,7 +4349,7 @@
         <v/>
       </c>
       <c r="BE16" s="19">
-        <f>IF($B16="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K16="Completed",$M16=""),"Completed visit missing Visit Notes",""),IF(AND($K16="Completed",$S16=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ16="Offer Sent",OR($X16="",$AA16="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ16="Active Negotiation",OR($AE16="",$AF16="",$AH16="",$AG16="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ16="Contract Sent",$AT16="",$R16=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ16="Contract Signed",$AU16=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ16="Long-Term Nurture",OR($AG16="",$AG16&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ16="Lost / Closed Out",OR($AR16="",$AS16="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM16="Sent",$AO16=""),"Gift marked Sent without recorded approval",""),IF($AX16="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B16="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K16="Completed",$M16=""),"Completed visit missing Visit Notes",""),IF(AND($K16="Completed",$S16=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ16="Offer Sent",OR($X16="",$AA16="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ16="Active Negotiation",OR($AE16="",$AF16="",$AH16="",$AG16="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ16="Contract Sent",$AT16="",$R16=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ16="Contract Signed",$AU16=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ16="Long-Term Nurture",OR($AG16="",$AG16&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ16="Lost / Closed Out",OR($AR16="",$AS16="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM16="Sent",OR($BH16="",$BI16="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX16="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF16" s="19" t="inlineStr">
@@ -4318,6 +4358,8 @@
         </is>
       </c>
       <c r="BG16" s="19" t="n"/>
+      <c r="BH16" s="19" t="n"/>
+      <c r="BI16" s="19" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
@@ -4487,7 +4529,7 @@
         <v/>
       </c>
       <c r="BE17" s="19">
-        <f>IF($B17="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K17="Completed",$M17=""),"Completed visit missing Visit Notes",""),IF(AND($K17="Completed",$S17=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ17="Offer Sent",OR($X17="",$AA17="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ17="Active Negotiation",OR($AE17="",$AF17="",$AH17="",$AG17="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ17="Contract Sent",$AT17="",$R17=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ17="Contract Signed",$AU17=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ17="Long-Term Nurture",OR($AG17="",$AG17&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ17="Lost / Closed Out",OR($AR17="",$AS17="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM17="Sent",$AO17=""),"Gift marked Sent without recorded approval",""),IF($AX17="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B17="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K17="Completed",$M17=""),"Completed visit missing Visit Notes",""),IF(AND($K17="Completed",$S17=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ17="Offer Sent",OR($X17="",$AA17="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ17="Active Negotiation",OR($AE17="",$AF17="",$AH17="",$AG17="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ17="Contract Sent",$AT17="",$R17=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ17="Contract Signed",$AU17=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ17="Long-Term Nurture",OR($AG17="",$AG17&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ17="Lost / Closed Out",OR($AR17="",$AS17="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM17="Sent",OR($BH17="",$BI17="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX17="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF17" s="19" t="inlineStr">
@@ -4496,6 +4538,8 @@
         </is>
       </c>
       <c r="BG17" s="19" t="n"/>
+      <c r="BH17" s="19" t="n"/>
+      <c r="BI17" s="19" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
@@ -4667,7 +4711,7 @@
         <v/>
       </c>
       <c r="BE18" s="19">
-        <f>IF($B18="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K18="Completed",$M18=""),"Completed visit missing Visit Notes",""),IF(AND($K18="Completed",$S18=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ18="Offer Sent",OR($X18="",$AA18="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ18="Active Negotiation",OR($AE18="",$AF18="",$AH18="",$AG18="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ18="Contract Sent",$AT18="",$R18=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ18="Contract Signed",$AU18=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ18="Long-Term Nurture",OR($AG18="",$AG18&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ18="Lost / Closed Out",OR($AR18="",$AS18="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM18="Sent",$AO18=""),"Gift marked Sent without recorded approval",""),IF($AX18="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B18="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K18="Completed",$M18=""),"Completed visit missing Visit Notes",""),IF(AND($K18="Completed",$S18=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ18="Offer Sent",OR($X18="",$AA18="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ18="Active Negotiation",OR($AE18="",$AF18="",$AH18="",$AG18="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ18="Contract Sent",$AT18="",$R18=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ18="Contract Signed",$AU18=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ18="Long-Term Nurture",OR($AG18="",$AG18&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ18="Lost / Closed Out",OR($AR18="",$AS18="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM18="Sent",OR($BH18="",$BI18="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX18="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF18" s="19" t="inlineStr">
@@ -4676,6 +4720,8 @@
         </is>
       </c>
       <c r="BG18" s="19" t="n"/>
+      <c r="BH18" s="19" t="n"/>
+      <c r="BI18" s="19" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
@@ -4819,7 +4865,7 @@
         <v/>
       </c>
       <c r="BE19" s="19">
-        <f>IF($B19="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K19="Completed",$M19=""),"Completed visit missing Visit Notes",""),IF(AND($K19="Completed",$S19=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ19="Offer Sent",OR($X19="",$AA19="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ19="Active Negotiation",OR($AE19="",$AF19="",$AH19="",$AG19="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ19="Contract Sent",$AT19="",$R19=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ19="Contract Signed",$AU19=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ19="Long-Term Nurture",OR($AG19="",$AG19&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ19="Lost / Closed Out",OR($AR19="",$AS19="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM19="Sent",$AO19=""),"Gift marked Sent without recorded approval",""),IF($AX19="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B19="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K19="Completed",$M19=""),"Completed visit missing Visit Notes",""),IF(AND($K19="Completed",$S19=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ19="Offer Sent",OR($X19="",$AA19="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ19="Active Negotiation",OR($AE19="",$AF19="",$AH19="",$AG19="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ19="Contract Sent",$AT19="",$R19=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ19="Contract Signed",$AU19=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ19="Long-Term Nurture",OR($AG19="",$AG19&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ19="Lost / Closed Out",OR($AR19="",$AS19="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM19="Sent",OR($BH19="",$BI19="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX19="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF19" s="19" t="inlineStr">
@@ -4828,6 +4874,8 @@
         </is>
       </c>
       <c r="BG19" s="19" t="n"/>
+      <c r="BH19" s="19" t="n"/>
+      <c r="BI19" s="19" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
@@ -4983,11 +5031,13 @@
         <v/>
       </c>
       <c r="BE20" s="19">
-        <f>IF($B20="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K20="Completed",$M20=""),"Completed visit missing Visit Notes",""),IF(AND($K20="Completed",$S20=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ20="Offer Sent",OR($X20="",$AA20="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ20="Active Negotiation",OR($AE20="",$AF20="",$AH20="",$AG20="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ20="Contract Sent",$AT20="",$R20=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ20="Contract Signed",$AU20=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ20="Long-Term Nurture",OR($AG20="",$AG20&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ20="Lost / Closed Out",OR($AR20="",$AS20="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM20="Sent",$AO20=""),"Gift marked Sent without recorded approval",""),IF($AX20="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B20="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K20="Completed",$M20=""),"Completed visit missing Visit Notes",""),IF(AND($K20="Completed",$S20=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ20="Offer Sent",OR($X20="",$AA20="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ20="Active Negotiation",OR($AE20="",$AF20="",$AH20="",$AG20="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ20="Contract Sent",$AT20="",$R20=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ20="Contract Signed",$AU20=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ20="Long-Term Nurture",OR($AG20="",$AG20&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ20="Lost / Closed Out",OR($AR20="",$AS20="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM20="Sent",OR($BH20="",$BI20="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX20="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
       <c r="BF20" s="19" t="n"/>
       <c r="BG20" s="19" t="n"/>
+      <c r="BH20" s="19" t="n"/>
+      <c r="BI20" s="19" t="n"/>
     </row>
     <row r="21">
       <c r="C21" s="2">
@@ -5023,7 +5073,7 @@
         <v/>
       </c>
       <c r="BE21" s="2">
-        <f>IF($B21="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K21="Completed",$M21=""),"Completed visit missing Visit Notes",""),IF(AND($K21="Completed",$S21=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ21="Offer Sent",OR($X21="",$AA21="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ21="Active Negotiation",OR($AE21="",$AF21="",$AH21="",$AG21="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ21="Contract Sent",$AT21="",$R21=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ21="Contract Signed",$AU21=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ21="Long-Term Nurture",OR($AG21="",$AG21&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ21="Lost / Closed Out",OR($AR21="",$AS21="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM21="Sent",$AO21=""),"Gift marked Sent without recorded approval",""),IF($AX21="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B21="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K21="Completed",$M21=""),"Completed visit missing Visit Notes",""),IF(AND($K21="Completed",$S21=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ21="Offer Sent",OR($X21="",$AA21="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ21="Active Negotiation",OR($AE21="",$AF21="",$AH21="",$AG21="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ21="Contract Sent",$AT21="",$R21=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ21="Contract Signed",$AU21=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ21="Long-Term Nurture",OR($AG21="",$AG21&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ21="Lost / Closed Out",OR($AR21="",$AS21="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM21="Sent",OR($BH21="",$BI21="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX21="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5061,7 +5111,7 @@
         <v/>
       </c>
       <c r="BE22" s="2">
-        <f>IF($B22="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K22="Completed",$M22=""),"Completed visit missing Visit Notes",""),IF(AND($K22="Completed",$S22=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ22="Offer Sent",OR($X22="",$AA22="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ22="Active Negotiation",OR($AE22="",$AF22="",$AH22="",$AG22="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ22="Contract Sent",$AT22="",$R22=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ22="Contract Signed",$AU22=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ22="Long-Term Nurture",OR($AG22="",$AG22&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ22="Lost / Closed Out",OR($AR22="",$AS22="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM22="Sent",$AO22=""),"Gift marked Sent without recorded approval",""),IF($AX22="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B22="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K22="Completed",$M22=""),"Completed visit missing Visit Notes",""),IF(AND($K22="Completed",$S22=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ22="Offer Sent",OR($X22="",$AA22="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ22="Active Negotiation",OR($AE22="",$AF22="",$AH22="",$AG22="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ22="Contract Sent",$AT22="",$R22=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ22="Contract Signed",$AU22=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ22="Long-Term Nurture",OR($AG22="",$AG22&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ22="Lost / Closed Out",OR($AR22="",$AS22="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM22="Sent",OR($BH22="",$BI22="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX22="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5099,7 +5149,7 @@
         <v/>
       </c>
       <c r="BE23" s="2">
-        <f>IF($B23="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K23="Completed",$M23=""),"Completed visit missing Visit Notes",""),IF(AND($K23="Completed",$S23=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ23="Offer Sent",OR($X23="",$AA23="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ23="Active Negotiation",OR($AE23="",$AF23="",$AH23="",$AG23="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ23="Contract Sent",$AT23="",$R23=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ23="Contract Signed",$AU23=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ23="Long-Term Nurture",OR($AG23="",$AG23&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ23="Lost / Closed Out",OR($AR23="",$AS23="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM23="Sent",$AO23=""),"Gift marked Sent without recorded approval",""),IF($AX23="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B23="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K23="Completed",$M23=""),"Completed visit missing Visit Notes",""),IF(AND($K23="Completed",$S23=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ23="Offer Sent",OR($X23="",$AA23="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ23="Active Negotiation",OR($AE23="",$AF23="",$AH23="",$AG23="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ23="Contract Sent",$AT23="",$R23=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ23="Contract Signed",$AU23=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ23="Long-Term Nurture",OR($AG23="",$AG23&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ23="Lost / Closed Out",OR($AR23="",$AS23="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM23="Sent",OR($BH23="",$BI23="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX23="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5137,7 +5187,7 @@
         <v/>
       </c>
       <c r="BE24" s="2">
-        <f>IF($B24="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K24="Completed",$M24=""),"Completed visit missing Visit Notes",""),IF(AND($K24="Completed",$S24=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ24="Offer Sent",OR($X24="",$AA24="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ24="Active Negotiation",OR($AE24="",$AF24="",$AH24="",$AG24="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ24="Contract Sent",$AT24="",$R24=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ24="Contract Signed",$AU24=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ24="Long-Term Nurture",OR($AG24="",$AG24&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ24="Lost / Closed Out",OR($AR24="",$AS24="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM24="Sent",$AO24=""),"Gift marked Sent without recorded approval",""),IF($AX24="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B24="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K24="Completed",$M24=""),"Completed visit missing Visit Notes",""),IF(AND($K24="Completed",$S24=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ24="Offer Sent",OR($X24="",$AA24="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ24="Active Negotiation",OR($AE24="",$AF24="",$AH24="",$AG24="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ24="Contract Sent",$AT24="",$R24=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ24="Contract Signed",$AU24=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ24="Long-Term Nurture",OR($AG24="",$AG24&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ24="Lost / Closed Out",OR($AR24="",$AS24="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM24="Sent",OR($BH24="",$BI24="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX24="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5175,7 +5225,7 @@
         <v/>
       </c>
       <c r="BE25" s="2">
-        <f>IF($B25="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K25="Completed",$M25=""),"Completed visit missing Visit Notes",""),IF(AND($K25="Completed",$S25=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ25="Offer Sent",OR($X25="",$AA25="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ25="Active Negotiation",OR($AE25="",$AF25="",$AH25="",$AG25="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ25="Contract Sent",$AT25="",$R25=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ25="Contract Signed",$AU25=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ25="Long-Term Nurture",OR($AG25="",$AG25&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ25="Lost / Closed Out",OR($AR25="",$AS25="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM25="Sent",$AO25=""),"Gift marked Sent without recorded approval",""),IF($AX25="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B25="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K25="Completed",$M25=""),"Completed visit missing Visit Notes",""),IF(AND($K25="Completed",$S25=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ25="Offer Sent",OR($X25="",$AA25="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ25="Active Negotiation",OR($AE25="",$AF25="",$AH25="",$AG25="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ25="Contract Sent",$AT25="",$R25=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ25="Contract Signed",$AU25=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ25="Long-Term Nurture",OR($AG25="",$AG25&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ25="Lost / Closed Out",OR($AR25="",$AS25="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM25="Sent",OR($BH25="",$BI25="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX25="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5213,7 +5263,7 @@
         <v/>
       </c>
       <c r="BE26" s="2">
-        <f>IF($B26="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K26="Completed",$M26=""),"Completed visit missing Visit Notes",""),IF(AND($K26="Completed",$S26=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ26="Offer Sent",OR($X26="",$AA26="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ26="Active Negotiation",OR($AE26="",$AF26="",$AH26="",$AG26="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ26="Contract Sent",$AT26="",$R26=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ26="Contract Signed",$AU26=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ26="Long-Term Nurture",OR($AG26="",$AG26&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ26="Lost / Closed Out",OR($AR26="",$AS26="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM26="Sent",$AO26=""),"Gift marked Sent without recorded approval",""),IF($AX26="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B26="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K26="Completed",$M26=""),"Completed visit missing Visit Notes",""),IF(AND($K26="Completed",$S26=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ26="Offer Sent",OR($X26="",$AA26="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ26="Active Negotiation",OR($AE26="",$AF26="",$AH26="",$AG26="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ26="Contract Sent",$AT26="",$R26=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ26="Contract Signed",$AU26=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ26="Long-Term Nurture",OR($AG26="",$AG26&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ26="Lost / Closed Out",OR($AR26="",$AS26="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM26="Sent",OR($BH26="",$BI26="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX26="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5251,7 +5301,7 @@
         <v/>
       </c>
       <c r="BE27" s="2">
-        <f>IF($B27="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K27="Completed",$M27=""),"Completed visit missing Visit Notes",""),IF(AND($K27="Completed",$S27=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ27="Offer Sent",OR($X27="",$AA27="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ27="Active Negotiation",OR($AE27="",$AF27="",$AH27="",$AG27="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ27="Contract Sent",$AT27="",$R27=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ27="Contract Signed",$AU27=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ27="Long-Term Nurture",OR($AG27="",$AG27&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ27="Lost / Closed Out",OR($AR27="",$AS27="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM27="Sent",$AO27=""),"Gift marked Sent without recorded approval",""),IF($AX27="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B27="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K27="Completed",$M27=""),"Completed visit missing Visit Notes",""),IF(AND($K27="Completed",$S27=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ27="Offer Sent",OR($X27="",$AA27="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ27="Active Negotiation",OR($AE27="",$AF27="",$AH27="",$AG27="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ27="Contract Sent",$AT27="",$R27=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ27="Contract Signed",$AU27=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ27="Long-Term Nurture",OR($AG27="",$AG27&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ27="Lost / Closed Out",OR($AR27="",$AS27="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM27="Sent",OR($BH27="",$BI27="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX27="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5289,7 +5339,7 @@
         <v/>
       </c>
       <c r="BE28" s="2">
-        <f>IF($B28="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K28="Completed",$M28=""),"Completed visit missing Visit Notes",""),IF(AND($K28="Completed",$S28=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ28="Offer Sent",OR($X28="",$AA28="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ28="Active Negotiation",OR($AE28="",$AF28="",$AH28="",$AG28="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ28="Contract Sent",$AT28="",$R28=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ28="Contract Signed",$AU28=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ28="Long-Term Nurture",OR($AG28="",$AG28&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ28="Lost / Closed Out",OR($AR28="",$AS28="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM28="Sent",$AO28=""),"Gift marked Sent without recorded approval",""),IF($AX28="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B28="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K28="Completed",$M28=""),"Completed visit missing Visit Notes",""),IF(AND($K28="Completed",$S28=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ28="Offer Sent",OR($X28="",$AA28="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ28="Active Negotiation",OR($AE28="",$AF28="",$AH28="",$AG28="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ28="Contract Sent",$AT28="",$R28=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ28="Contract Signed",$AU28=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ28="Long-Term Nurture",OR($AG28="",$AG28&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ28="Lost / Closed Out",OR($AR28="",$AS28="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM28="Sent",OR($BH28="",$BI28="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX28="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5327,7 +5377,7 @@
         <v/>
       </c>
       <c r="BE29" s="2">
-        <f>IF($B29="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K29="Completed",$M29=""),"Completed visit missing Visit Notes",""),IF(AND($K29="Completed",$S29=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ29="Offer Sent",OR($X29="",$AA29="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ29="Active Negotiation",OR($AE29="",$AF29="",$AH29="",$AG29="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ29="Contract Sent",$AT29="",$R29=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ29="Contract Signed",$AU29=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ29="Long-Term Nurture",OR($AG29="",$AG29&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ29="Lost / Closed Out",OR($AR29="",$AS29="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM29="Sent",$AO29=""),"Gift marked Sent without recorded approval",""),IF($AX29="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B29="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K29="Completed",$M29=""),"Completed visit missing Visit Notes",""),IF(AND($K29="Completed",$S29=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ29="Offer Sent",OR($X29="",$AA29="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ29="Active Negotiation",OR($AE29="",$AF29="",$AH29="",$AG29="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ29="Contract Sent",$AT29="",$R29=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ29="Contract Signed",$AU29=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ29="Long-Term Nurture",OR($AG29="",$AG29&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ29="Lost / Closed Out",OR($AR29="",$AS29="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM29="Sent",OR($BH29="",$BI29="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX29="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5365,7 +5415,7 @@
         <v/>
       </c>
       <c r="BE30" s="2">
-        <f>IF($B30="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K30="Completed",$M30=""),"Completed visit missing Visit Notes",""),IF(AND($K30="Completed",$S30=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ30="Offer Sent",OR($X30="",$AA30="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ30="Active Negotiation",OR($AE30="",$AF30="",$AH30="",$AG30="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ30="Contract Sent",$AT30="",$R30=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ30="Contract Signed",$AU30=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ30="Long-Term Nurture",OR($AG30="",$AG30&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ30="Lost / Closed Out",OR($AR30="",$AS30="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM30="Sent",$AO30=""),"Gift marked Sent without recorded approval",""),IF($AX30="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B30="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K30="Completed",$M30=""),"Completed visit missing Visit Notes",""),IF(AND($K30="Completed",$S30=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ30="Offer Sent",OR($X30="",$AA30="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ30="Active Negotiation",OR($AE30="",$AF30="",$AH30="",$AG30="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ30="Contract Sent",$AT30="",$R30=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ30="Contract Signed",$AU30=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ30="Long-Term Nurture",OR($AG30="",$AG30&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ30="Lost / Closed Out",OR($AR30="",$AS30="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM30="Sent",OR($BH30="",$BI30="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX30="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5403,7 +5453,7 @@
         <v/>
       </c>
       <c r="BE31" s="2">
-        <f>IF($B31="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K31="Completed",$M31=""),"Completed visit missing Visit Notes",""),IF(AND($K31="Completed",$S31=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ31="Offer Sent",OR($X31="",$AA31="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ31="Active Negotiation",OR($AE31="",$AF31="",$AH31="",$AG31="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ31="Contract Sent",$AT31="",$R31=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ31="Contract Signed",$AU31=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ31="Long-Term Nurture",OR($AG31="",$AG31&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ31="Lost / Closed Out",OR($AR31="",$AS31="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM31="Sent",$AO31=""),"Gift marked Sent without recorded approval",""),IF($AX31="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B31="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K31="Completed",$M31=""),"Completed visit missing Visit Notes",""),IF(AND($K31="Completed",$S31=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ31="Offer Sent",OR($X31="",$AA31="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ31="Active Negotiation",OR($AE31="",$AF31="",$AH31="",$AG31="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ31="Contract Sent",$AT31="",$R31=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ31="Contract Signed",$AU31=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ31="Long-Term Nurture",OR($AG31="",$AG31&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ31="Lost / Closed Out",OR($AR31="",$AS31="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM31="Sent",OR($BH31="",$BI31="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX31="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5441,7 +5491,7 @@
         <v/>
       </c>
       <c r="BE32" s="2">
-        <f>IF($B32="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K32="Completed",$M32=""),"Completed visit missing Visit Notes",""),IF(AND($K32="Completed",$S32=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ32="Offer Sent",OR($X32="",$AA32="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ32="Active Negotiation",OR($AE32="",$AF32="",$AH32="",$AG32="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ32="Contract Sent",$AT32="",$R32=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ32="Contract Signed",$AU32=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ32="Long-Term Nurture",OR($AG32="",$AG32&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ32="Lost / Closed Out",OR($AR32="",$AS32="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM32="Sent",$AO32=""),"Gift marked Sent without recorded approval",""),IF($AX32="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B32="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K32="Completed",$M32=""),"Completed visit missing Visit Notes",""),IF(AND($K32="Completed",$S32=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ32="Offer Sent",OR($X32="",$AA32="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ32="Active Negotiation",OR($AE32="",$AF32="",$AH32="",$AG32="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ32="Contract Sent",$AT32="",$R32=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ32="Contract Signed",$AU32=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ32="Long-Term Nurture",OR($AG32="",$AG32&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ32="Lost / Closed Out",OR($AR32="",$AS32="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM32="Sent",OR($BH32="",$BI32="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX32="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5479,7 +5529,7 @@
         <v/>
       </c>
       <c r="BE33" s="2">
-        <f>IF($B33="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K33="Completed",$M33=""),"Completed visit missing Visit Notes",""),IF(AND($K33="Completed",$S33=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ33="Offer Sent",OR($X33="",$AA33="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ33="Active Negotiation",OR($AE33="",$AF33="",$AH33="",$AG33="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ33="Contract Sent",$AT33="",$R33=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ33="Contract Signed",$AU33=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ33="Long-Term Nurture",OR($AG33="",$AG33&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ33="Lost / Closed Out",OR($AR33="",$AS33="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM33="Sent",$AO33=""),"Gift marked Sent without recorded approval",""),IF($AX33="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B33="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K33="Completed",$M33=""),"Completed visit missing Visit Notes",""),IF(AND($K33="Completed",$S33=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ33="Offer Sent",OR($X33="",$AA33="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ33="Active Negotiation",OR($AE33="",$AF33="",$AH33="",$AG33="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ33="Contract Sent",$AT33="",$R33=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ33="Contract Signed",$AU33=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ33="Long-Term Nurture",OR($AG33="",$AG33&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ33="Lost / Closed Out",OR($AR33="",$AS33="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM33="Sent",OR($BH33="",$BI33="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX33="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5517,7 +5567,7 @@
         <v/>
       </c>
       <c r="BE34" s="2">
-        <f>IF($B34="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K34="Completed",$M34=""),"Completed visit missing Visit Notes",""),IF(AND($K34="Completed",$S34=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ34="Offer Sent",OR($X34="",$AA34="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ34="Active Negotiation",OR($AE34="",$AF34="",$AH34="",$AG34="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ34="Contract Sent",$AT34="",$R34=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ34="Contract Signed",$AU34=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ34="Long-Term Nurture",OR($AG34="",$AG34&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ34="Lost / Closed Out",OR($AR34="",$AS34="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM34="Sent",$AO34=""),"Gift marked Sent without recorded approval",""),IF($AX34="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B34="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K34="Completed",$M34=""),"Completed visit missing Visit Notes",""),IF(AND($K34="Completed",$S34=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ34="Offer Sent",OR($X34="",$AA34="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ34="Active Negotiation",OR($AE34="",$AF34="",$AH34="",$AG34="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ34="Contract Sent",$AT34="",$R34=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ34="Contract Signed",$AU34=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ34="Long-Term Nurture",OR($AG34="",$AG34&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ34="Lost / Closed Out",OR($AR34="",$AS34="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM34="Sent",OR($BH34="",$BI34="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX34="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5555,7 +5605,7 @@
         <v/>
       </c>
       <c r="BE35" s="2">
-        <f>IF($B35="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K35="Completed",$M35=""),"Completed visit missing Visit Notes",""),IF(AND($K35="Completed",$S35=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ35="Offer Sent",OR($X35="",$AA35="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ35="Active Negotiation",OR($AE35="",$AF35="",$AH35="",$AG35="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ35="Contract Sent",$AT35="",$R35=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ35="Contract Signed",$AU35=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ35="Long-Term Nurture",OR($AG35="",$AG35&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ35="Lost / Closed Out",OR($AR35="",$AS35="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM35="Sent",$AO35=""),"Gift marked Sent without recorded approval",""),IF($AX35="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B35="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K35="Completed",$M35=""),"Completed visit missing Visit Notes",""),IF(AND($K35="Completed",$S35=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ35="Offer Sent",OR($X35="",$AA35="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ35="Active Negotiation",OR($AE35="",$AF35="",$AH35="",$AG35="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ35="Contract Sent",$AT35="",$R35=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ35="Contract Signed",$AU35=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ35="Long-Term Nurture",OR($AG35="",$AG35&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ35="Lost / Closed Out",OR($AR35="",$AS35="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM35="Sent",OR($BH35="",$BI35="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX35="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5593,7 +5643,7 @@
         <v/>
       </c>
       <c r="BE36" s="2">
-        <f>IF($B36="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K36="Completed",$M36=""),"Completed visit missing Visit Notes",""),IF(AND($K36="Completed",$S36=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ36="Offer Sent",OR($X36="",$AA36="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ36="Active Negotiation",OR($AE36="",$AF36="",$AH36="",$AG36="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ36="Contract Sent",$AT36="",$R36=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ36="Contract Signed",$AU36=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ36="Long-Term Nurture",OR($AG36="",$AG36&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ36="Lost / Closed Out",OR($AR36="",$AS36="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM36="Sent",$AO36=""),"Gift marked Sent without recorded approval",""),IF($AX36="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B36="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K36="Completed",$M36=""),"Completed visit missing Visit Notes",""),IF(AND($K36="Completed",$S36=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ36="Offer Sent",OR($X36="",$AA36="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ36="Active Negotiation",OR($AE36="",$AF36="",$AH36="",$AG36="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ36="Contract Sent",$AT36="",$R36=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ36="Contract Signed",$AU36=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ36="Long-Term Nurture",OR($AG36="",$AG36&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ36="Lost / Closed Out",OR($AR36="",$AS36="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM36="Sent",OR($BH36="",$BI36="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX36="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5631,7 +5681,7 @@
         <v/>
       </c>
       <c r="BE37" s="2">
-        <f>IF($B37="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K37="Completed",$M37=""),"Completed visit missing Visit Notes",""),IF(AND($K37="Completed",$S37=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ37="Offer Sent",OR($X37="",$AA37="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ37="Active Negotiation",OR($AE37="",$AF37="",$AH37="",$AG37="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ37="Contract Sent",$AT37="",$R37=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ37="Contract Signed",$AU37=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ37="Long-Term Nurture",OR($AG37="",$AG37&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ37="Lost / Closed Out",OR($AR37="",$AS37="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM37="Sent",$AO37=""),"Gift marked Sent without recorded approval",""),IF($AX37="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B37="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K37="Completed",$M37=""),"Completed visit missing Visit Notes",""),IF(AND($K37="Completed",$S37=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ37="Offer Sent",OR($X37="",$AA37="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ37="Active Negotiation",OR($AE37="",$AF37="",$AH37="",$AG37="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ37="Contract Sent",$AT37="",$R37=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ37="Contract Signed",$AU37=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ37="Long-Term Nurture",OR($AG37="",$AG37&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ37="Lost / Closed Out",OR($AR37="",$AS37="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM37="Sent",OR($BH37="",$BI37="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX37="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5669,7 +5719,7 @@
         <v/>
       </c>
       <c r="BE38" s="2">
-        <f>IF($B38="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K38="Completed",$M38=""),"Completed visit missing Visit Notes",""),IF(AND($K38="Completed",$S38=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ38="Offer Sent",OR($X38="",$AA38="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ38="Active Negotiation",OR($AE38="",$AF38="",$AH38="",$AG38="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ38="Contract Sent",$AT38="",$R38=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ38="Contract Signed",$AU38=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ38="Long-Term Nurture",OR($AG38="",$AG38&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ38="Lost / Closed Out",OR($AR38="",$AS38="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM38="Sent",$AO38=""),"Gift marked Sent without recorded approval",""),IF($AX38="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B38="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K38="Completed",$M38=""),"Completed visit missing Visit Notes",""),IF(AND($K38="Completed",$S38=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ38="Offer Sent",OR($X38="",$AA38="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ38="Active Negotiation",OR($AE38="",$AF38="",$AH38="",$AG38="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ38="Contract Sent",$AT38="",$R38=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ38="Contract Signed",$AU38=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ38="Long-Term Nurture",OR($AG38="",$AG38&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ38="Lost / Closed Out",OR($AR38="",$AS38="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM38="Sent",OR($BH38="",$BI38="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX38="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5707,7 +5757,7 @@
         <v/>
       </c>
       <c r="BE39" s="2">
-        <f>IF($B39="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K39="Completed",$M39=""),"Completed visit missing Visit Notes",""),IF(AND($K39="Completed",$S39=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ39="Offer Sent",OR($X39="",$AA39="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ39="Active Negotiation",OR($AE39="",$AF39="",$AH39="",$AG39="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ39="Contract Sent",$AT39="",$R39=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ39="Contract Signed",$AU39=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ39="Long-Term Nurture",OR($AG39="",$AG39&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ39="Lost / Closed Out",OR($AR39="",$AS39="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM39="Sent",$AO39=""),"Gift marked Sent without recorded approval",""),IF($AX39="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B39="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K39="Completed",$M39=""),"Completed visit missing Visit Notes",""),IF(AND($K39="Completed",$S39=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ39="Offer Sent",OR($X39="",$AA39="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ39="Active Negotiation",OR($AE39="",$AF39="",$AH39="",$AG39="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ39="Contract Sent",$AT39="",$R39=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ39="Contract Signed",$AU39=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ39="Long-Term Nurture",OR($AG39="",$AG39&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ39="Lost / Closed Out",OR($AR39="",$AS39="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM39="Sent",OR($BH39="",$BI39="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX39="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5745,7 +5795,7 @@
         <v/>
       </c>
       <c r="BE40" s="2">
-        <f>IF($B40="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K40="Completed",$M40=""),"Completed visit missing Visit Notes",""),IF(AND($K40="Completed",$S40=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ40="Offer Sent",OR($X40="",$AA40="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ40="Active Negotiation",OR($AE40="",$AF40="",$AH40="",$AG40="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ40="Contract Sent",$AT40="",$R40=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ40="Contract Signed",$AU40=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ40="Long-Term Nurture",OR($AG40="",$AG40&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ40="Lost / Closed Out",OR($AR40="",$AS40="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM40="Sent",$AO40=""),"Gift marked Sent without recorded approval",""),IF($AX40="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B40="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K40="Completed",$M40=""),"Completed visit missing Visit Notes",""),IF(AND($K40="Completed",$S40=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ40="Offer Sent",OR($X40="",$AA40="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ40="Active Negotiation",OR($AE40="",$AF40="",$AH40="",$AG40="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ40="Contract Sent",$AT40="",$R40=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ40="Contract Signed",$AU40=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ40="Long-Term Nurture",OR($AG40="",$AG40&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ40="Lost / Closed Out",OR($AR40="",$AS40="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM40="Sent",OR($BH40="",$BI40="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX40="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5783,7 +5833,7 @@
         <v/>
       </c>
       <c r="BE41" s="2">
-        <f>IF($B41="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K41="Completed",$M41=""),"Completed visit missing Visit Notes",""),IF(AND($K41="Completed",$S41=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ41="Offer Sent",OR($X41="",$AA41="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ41="Active Negotiation",OR($AE41="",$AF41="",$AH41="",$AG41="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ41="Contract Sent",$AT41="",$R41=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ41="Contract Signed",$AU41=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ41="Long-Term Nurture",OR($AG41="",$AG41&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ41="Lost / Closed Out",OR($AR41="",$AS41="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM41="Sent",$AO41=""),"Gift marked Sent without recorded approval",""),IF($AX41="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B41="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K41="Completed",$M41=""),"Completed visit missing Visit Notes",""),IF(AND($K41="Completed",$S41=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ41="Offer Sent",OR($X41="",$AA41="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ41="Active Negotiation",OR($AE41="",$AF41="",$AH41="",$AG41="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ41="Contract Sent",$AT41="",$R41=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ41="Contract Signed",$AU41=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ41="Long-Term Nurture",OR($AG41="",$AG41&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ41="Lost / Closed Out",OR($AR41="",$AS41="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM41="Sent",OR($BH41="",$BI41="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX41="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5821,7 +5871,7 @@
         <v/>
       </c>
       <c r="BE42" s="2">
-        <f>IF($B42="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K42="Completed",$M42=""),"Completed visit missing Visit Notes",""),IF(AND($K42="Completed",$S42=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ42="Offer Sent",OR($X42="",$AA42="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ42="Active Negotiation",OR($AE42="",$AF42="",$AH42="",$AG42="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ42="Contract Sent",$AT42="",$R42=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ42="Contract Signed",$AU42=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ42="Long-Term Nurture",OR($AG42="",$AG42&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ42="Lost / Closed Out",OR($AR42="",$AS42="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM42="Sent",$AO42=""),"Gift marked Sent without recorded approval",""),IF($AX42="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B42="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K42="Completed",$M42=""),"Completed visit missing Visit Notes",""),IF(AND($K42="Completed",$S42=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ42="Offer Sent",OR($X42="",$AA42="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ42="Active Negotiation",OR($AE42="",$AF42="",$AH42="",$AG42="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ42="Contract Sent",$AT42="",$R42=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ42="Contract Signed",$AU42=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ42="Long-Term Nurture",OR($AG42="",$AG42&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ42="Lost / Closed Out",OR($AR42="",$AS42="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM42="Sent",OR($BH42="",$BI42="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX42="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5859,7 +5909,7 @@
         <v/>
       </c>
       <c r="BE43" s="2">
-        <f>IF($B43="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K43="Completed",$M43=""),"Completed visit missing Visit Notes",""),IF(AND($K43="Completed",$S43=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ43="Offer Sent",OR($X43="",$AA43="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ43="Active Negotiation",OR($AE43="",$AF43="",$AH43="",$AG43="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ43="Contract Sent",$AT43="",$R43=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ43="Contract Signed",$AU43=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ43="Long-Term Nurture",OR($AG43="",$AG43&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ43="Lost / Closed Out",OR($AR43="",$AS43="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM43="Sent",$AO43=""),"Gift marked Sent without recorded approval",""),IF($AX43="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B43="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K43="Completed",$M43=""),"Completed visit missing Visit Notes",""),IF(AND($K43="Completed",$S43=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ43="Offer Sent",OR($X43="",$AA43="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ43="Active Negotiation",OR($AE43="",$AF43="",$AH43="",$AG43="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ43="Contract Sent",$AT43="",$R43=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ43="Contract Signed",$AU43=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ43="Long-Term Nurture",OR($AG43="",$AG43&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ43="Lost / Closed Out",OR($AR43="",$AS43="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM43="Sent",OR($BH43="",$BI43="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX43="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5897,7 +5947,7 @@
         <v/>
       </c>
       <c r="BE44" s="2">
-        <f>IF($B44="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K44="Completed",$M44=""),"Completed visit missing Visit Notes",""),IF(AND($K44="Completed",$S44=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ44="Offer Sent",OR($X44="",$AA44="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ44="Active Negotiation",OR($AE44="",$AF44="",$AH44="",$AG44="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ44="Contract Sent",$AT44="",$R44=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ44="Contract Signed",$AU44=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ44="Long-Term Nurture",OR($AG44="",$AG44&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ44="Lost / Closed Out",OR($AR44="",$AS44="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM44="Sent",$AO44=""),"Gift marked Sent without recorded approval",""),IF($AX44="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B44="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K44="Completed",$M44=""),"Completed visit missing Visit Notes",""),IF(AND($K44="Completed",$S44=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ44="Offer Sent",OR($X44="",$AA44="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ44="Active Negotiation",OR($AE44="",$AF44="",$AH44="",$AG44="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ44="Contract Sent",$AT44="",$R44=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ44="Contract Signed",$AU44=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ44="Long-Term Nurture",OR($AG44="",$AG44&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ44="Lost / Closed Out",OR($AR44="",$AS44="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM44="Sent",OR($BH44="",$BI44="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX44="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5935,7 +5985,7 @@
         <v/>
       </c>
       <c r="BE45" s="2">
-        <f>IF($B45="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K45="Completed",$M45=""),"Completed visit missing Visit Notes",""),IF(AND($K45="Completed",$S45=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ45="Offer Sent",OR($X45="",$AA45="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ45="Active Negotiation",OR($AE45="",$AF45="",$AH45="",$AG45="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ45="Contract Sent",$AT45="",$R45=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ45="Contract Signed",$AU45=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ45="Long-Term Nurture",OR($AG45="",$AG45&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ45="Lost / Closed Out",OR($AR45="",$AS45="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM45="Sent",$AO45=""),"Gift marked Sent without recorded approval",""),IF($AX45="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B45="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K45="Completed",$M45=""),"Completed visit missing Visit Notes",""),IF(AND($K45="Completed",$S45=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ45="Offer Sent",OR($X45="",$AA45="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ45="Active Negotiation",OR($AE45="",$AF45="",$AH45="",$AG45="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ45="Contract Sent",$AT45="",$R45=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ45="Contract Signed",$AU45=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ45="Long-Term Nurture",OR($AG45="",$AG45&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ45="Lost / Closed Out",OR($AR45="",$AS45="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM45="Sent",OR($BH45="",$BI45="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX45="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -5973,7 +6023,7 @@
         <v/>
       </c>
       <c r="BE46" s="2">
-        <f>IF($B46="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K46="Completed",$M46=""),"Completed visit missing Visit Notes",""),IF(AND($K46="Completed",$S46=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ46="Offer Sent",OR($X46="",$AA46="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ46="Active Negotiation",OR($AE46="",$AF46="",$AH46="",$AG46="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ46="Contract Sent",$AT46="",$R46=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ46="Contract Signed",$AU46=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ46="Long-Term Nurture",OR($AG46="",$AG46&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ46="Lost / Closed Out",OR($AR46="",$AS46="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM46="Sent",$AO46=""),"Gift marked Sent without recorded approval",""),IF($AX46="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B46="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K46="Completed",$M46=""),"Completed visit missing Visit Notes",""),IF(AND($K46="Completed",$S46=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ46="Offer Sent",OR($X46="",$AA46="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ46="Active Negotiation",OR($AE46="",$AF46="",$AH46="",$AG46="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ46="Contract Sent",$AT46="",$R46=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ46="Contract Signed",$AU46=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ46="Long-Term Nurture",OR($AG46="",$AG46&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ46="Lost / Closed Out",OR($AR46="",$AS46="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM46="Sent",OR($BH46="",$BI46="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX46="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6011,7 +6061,7 @@
         <v/>
       </c>
       <c r="BE47" s="2">
-        <f>IF($B47="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K47="Completed",$M47=""),"Completed visit missing Visit Notes",""),IF(AND($K47="Completed",$S47=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ47="Offer Sent",OR($X47="",$AA47="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ47="Active Negotiation",OR($AE47="",$AF47="",$AH47="",$AG47="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ47="Contract Sent",$AT47="",$R47=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ47="Contract Signed",$AU47=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ47="Long-Term Nurture",OR($AG47="",$AG47&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ47="Lost / Closed Out",OR($AR47="",$AS47="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM47="Sent",$AO47=""),"Gift marked Sent without recorded approval",""),IF($AX47="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B47="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K47="Completed",$M47=""),"Completed visit missing Visit Notes",""),IF(AND($K47="Completed",$S47=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ47="Offer Sent",OR($X47="",$AA47="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ47="Active Negotiation",OR($AE47="",$AF47="",$AH47="",$AG47="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ47="Contract Sent",$AT47="",$R47=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ47="Contract Signed",$AU47=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ47="Long-Term Nurture",OR($AG47="",$AG47&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ47="Lost / Closed Out",OR($AR47="",$AS47="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM47="Sent",OR($BH47="",$BI47="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX47="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6049,7 +6099,7 @@
         <v/>
       </c>
       <c r="BE48" s="2">
-        <f>IF($B48="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K48="Completed",$M48=""),"Completed visit missing Visit Notes",""),IF(AND($K48="Completed",$S48=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ48="Offer Sent",OR($X48="",$AA48="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ48="Active Negotiation",OR($AE48="",$AF48="",$AH48="",$AG48="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ48="Contract Sent",$AT48="",$R48=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ48="Contract Signed",$AU48=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ48="Long-Term Nurture",OR($AG48="",$AG48&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ48="Lost / Closed Out",OR($AR48="",$AS48="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM48="Sent",$AO48=""),"Gift marked Sent without recorded approval",""),IF($AX48="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B48="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K48="Completed",$M48=""),"Completed visit missing Visit Notes",""),IF(AND($K48="Completed",$S48=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ48="Offer Sent",OR($X48="",$AA48="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ48="Active Negotiation",OR($AE48="",$AF48="",$AH48="",$AG48="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ48="Contract Sent",$AT48="",$R48=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ48="Contract Signed",$AU48=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ48="Long-Term Nurture",OR($AG48="",$AG48&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ48="Lost / Closed Out",OR($AR48="",$AS48="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM48="Sent",OR($BH48="",$BI48="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX48="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6087,7 +6137,7 @@
         <v/>
       </c>
       <c r="BE49" s="2">
-        <f>IF($B49="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K49="Completed",$M49=""),"Completed visit missing Visit Notes",""),IF(AND($K49="Completed",$S49=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ49="Offer Sent",OR($X49="",$AA49="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ49="Active Negotiation",OR($AE49="",$AF49="",$AH49="",$AG49="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ49="Contract Sent",$AT49="",$R49=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ49="Contract Signed",$AU49=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ49="Long-Term Nurture",OR($AG49="",$AG49&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ49="Lost / Closed Out",OR($AR49="",$AS49="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM49="Sent",$AO49=""),"Gift marked Sent without recorded approval",""),IF($AX49="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B49="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K49="Completed",$M49=""),"Completed visit missing Visit Notes",""),IF(AND($K49="Completed",$S49=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ49="Offer Sent",OR($X49="",$AA49="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ49="Active Negotiation",OR($AE49="",$AF49="",$AH49="",$AG49="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ49="Contract Sent",$AT49="",$R49=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ49="Contract Signed",$AU49=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ49="Long-Term Nurture",OR($AG49="",$AG49&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ49="Lost / Closed Out",OR($AR49="",$AS49="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM49="Sent",OR($BH49="",$BI49="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX49="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6125,7 +6175,7 @@
         <v/>
       </c>
       <c r="BE50" s="2">
-        <f>IF($B50="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K50="Completed",$M50=""),"Completed visit missing Visit Notes",""),IF(AND($K50="Completed",$S50=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ50="Offer Sent",OR($X50="",$AA50="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ50="Active Negotiation",OR($AE50="",$AF50="",$AH50="",$AG50="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ50="Contract Sent",$AT50="",$R50=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ50="Contract Signed",$AU50=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ50="Long-Term Nurture",OR($AG50="",$AG50&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ50="Lost / Closed Out",OR($AR50="",$AS50="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM50="Sent",$AO50=""),"Gift marked Sent without recorded approval",""),IF($AX50="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B50="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K50="Completed",$M50=""),"Completed visit missing Visit Notes",""),IF(AND($K50="Completed",$S50=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ50="Offer Sent",OR($X50="",$AA50="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ50="Active Negotiation",OR($AE50="",$AF50="",$AH50="",$AG50="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ50="Contract Sent",$AT50="",$R50=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ50="Contract Signed",$AU50=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ50="Long-Term Nurture",OR($AG50="",$AG50&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ50="Lost / Closed Out",OR($AR50="",$AS50="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM50="Sent",OR($BH50="",$BI50="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX50="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6163,7 +6213,7 @@
         <v/>
       </c>
       <c r="BE51" s="2">
-        <f>IF($B51="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K51="Completed",$M51=""),"Completed visit missing Visit Notes",""),IF(AND($K51="Completed",$S51=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ51="Offer Sent",OR($X51="",$AA51="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ51="Active Negotiation",OR($AE51="",$AF51="",$AH51="",$AG51="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ51="Contract Sent",$AT51="",$R51=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ51="Contract Signed",$AU51=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ51="Long-Term Nurture",OR($AG51="",$AG51&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ51="Lost / Closed Out",OR($AR51="",$AS51="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM51="Sent",$AO51=""),"Gift marked Sent without recorded approval",""),IF($AX51="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B51="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K51="Completed",$M51=""),"Completed visit missing Visit Notes",""),IF(AND($K51="Completed",$S51=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ51="Offer Sent",OR($X51="",$AA51="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ51="Active Negotiation",OR($AE51="",$AF51="",$AH51="",$AG51="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ51="Contract Sent",$AT51="",$R51=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ51="Contract Signed",$AU51=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ51="Long-Term Nurture",OR($AG51="",$AG51&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ51="Lost / Closed Out",OR($AR51="",$AS51="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM51="Sent",OR($BH51="",$BI51="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX51="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6201,7 +6251,7 @@
         <v/>
       </c>
       <c r="BE52" s="2">
-        <f>IF($B52="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K52="Completed",$M52=""),"Completed visit missing Visit Notes",""),IF(AND($K52="Completed",$S52=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ52="Offer Sent",OR($X52="",$AA52="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ52="Active Negotiation",OR($AE52="",$AF52="",$AH52="",$AG52="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ52="Contract Sent",$AT52="",$R52=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ52="Contract Signed",$AU52=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ52="Long-Term Nurture",OR($AG52="",$AG52&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ52="Lost / Closed Out",OR($AR52="",$AS52="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM52="Sent",$AO52=""),"Gift marked Sent without recorded approval",""),IF($AX52="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B52="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K52="Completed",$M52=""),"Completed visit missing Visit Notes",""),IF(AND($K52="Completed",$S52=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ52="Offer Sent",OR($X52="",$AA52="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ52="Active Negotiation",OR($AE52="",$AF52="",$AH52="",$AG52="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ52="Contract Sent",$AT52="",$R52=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ52="Contract Signed",$AU52=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ52="Long-Term Nurture",OR($AG52="",$AG52&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ52="Lost / Closed Out",OR($AR52="",$AS52="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM52="Sent",OR($BH52="",$BI52="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX52="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6239,7 +6289,7 @@
         <v/>
       </c>
       <c r="BE53" s="2">
-        <f>IF($B53="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K53="Completed",$M53=""),"Completed visit missing Visit Notes",""),IF(AND($K53="Completed",$S53=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ53="Offer Sent",OR($X53="",$AA53="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ53="Active Negotiation",OR($AE53="",$AF53="",$AH53="",$AG53="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ53="Contract Sent",$AT53="",$R53=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ53="Contract Signed",$AU53=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ53="Long-Term Nurture",OR($AG53="",$AG53&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ53="Lost / Closed Out",OR($AR53="",$AS53="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM53="Sent",$AO53=""),"Gift marked Sent without recorded approval",""),IF($AX53="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B53="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K53="Completed",$M53=""),"Completed visit missing Visit Notes",""),IF(AND($K53="Completed",$S53=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ53="Offer Sent",OR($X53="",$AA53="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ53="Active Negotiation",OR($AE53="",$AF53="",$AH53="",$AG53="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ53="Contract Sent",$AT53="",$R53=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ53="Contract Signed",$AU53=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ53="Long-Term Nurture",OR($AG53="",$AG53&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ53="Lost / Closed Out",OR($AR53="",$AS53="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM53="Sent",OR($BH53="",$BI53="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX53="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6277,7 +6327,7 @@
         <v/>
       </c>
       <c r="BE54" s="2">
-        <f>IF($B54="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K54="Completed",$M54=""),"Completed visit missing Visit Notes",""),IF(AND($K54="Completed",$S54=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ54="Offer Sent",OR($X54="",$AA54="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ54="Active Negotiation",OR($AE54="",$AF54="",$AH54="",$AG54="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ54="Contract Sent",$AT54="",$R54=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ54="Contract Signed",$AU54=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ54="Long-Term Nurture",OR($AG54="",$AG54&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ54="Lost / Closed Out",OR($AR54="",$AS54="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM54="Sent",$AO54=""),"Gift marked Sent without recorded approval",""),IF($AX54="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B54="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K54="Completed",$M54=""),"Completed visit missing Visit Notes",""),IF(AND($K54="Completed",$S54=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ54="Offer Sent",OR($X54="",$AA54="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ54="Active Negotiation",OR($AE54="",$AF54="",$AH54="",$AG54="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ54="Contract Sent",$AT54="",$R54=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ54="Contract Signed",$AU54=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ54="Long-Term Nurture",OR($AG54="",$AG54&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ54="Lost / Closed Out",OR($AR54="",$AS54="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM54="Sent",OR($BH54="",$BI54="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX54="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6315,7 +6365,7 @@
         <v/>
       </c>
       <c r="BE55" s="2">
-        <f>IF($B55="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K55="Completed",$M55=""),"Completed visit missing Visit Notes",""),IF(AND($K55="Completed",$S55=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ55="Offer Sent",OR($X55="",$AA55="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ55="Active Negotiation",OR($AE55="",$AF55="",$AH55="",$AG55="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ55="Contract Sent",$AT55="",$R55=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ55="Contract Signed",$AU55=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ55="Long-Term Nurture",OR($AG55="",$AG55&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ55="Lost / Closed Out",OR($AR55="",$AS55="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM55="Sent",$AO55=""),"Gift marked Sent without recorded approval",""),IF($AX55="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B55="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K55="Completed",$M55=""),"Completed visit missing Visit Notes",""),IF(AND($K55="Completed",$S55=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ55="Offer Sent",OR($X55="",$AA55="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ55="Active Negotiation",OR($AE55="",$AF55="",$AH55="",$AG55="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ55="Contract Sent",$AT55="",$R55=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ55="Contract Signed",$AU55=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ55="Long-Term Nurture",OR($AG55="",$AG55&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ55="Lost / Closed Out",OR($AR55="",$AS55="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM55="Sent",OR($BH55="",$BI55="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX55="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6353,7 +6403,7 @@
         <v/>
       </c>
       <c r="BE56" s="2">
-        <f>IF($B56="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K56="Completed",$M56=""),"Completed visit missing Visit Notes",""),IF(AND($K56="Completed",$S56=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ56="Offer Sent",OR($X56="",$AA56="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ56="Active Negotiation",OR($AE56="",$AF56="",$AH56="",$AG56="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ56="Contract Sent",$AT56="",$R56=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ56="Contract Signed",$AU56=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ56="Long-Term Nurture",OR($AG56="",$AG56&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ56="Lost / Closed Out",OR($AR56="",$AS56="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM56="Sent",$AO56=""),"Gift marked Sent without recorded approval",""),IF($AX56="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B56="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K56="Completed",$M56=""),"Completed visit missing Visit Notes",""),IF(AND($K56="Completed",$S56=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ56="Offer Sent",OR($X56="",$AA56="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ56="Active Negotiation",OR($AE56="",$AF56="",$AH56="",$AG56="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ56="Contract Sent",$AT56="",$R56=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ56="Contract Signed",$AU56=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ56="Long-Term Nurture",OR($AG56="",$AG56&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ56="Lost / Closed Out",OR($AR56="",$AS56="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM56="Sent",OR($BH56="",$BI56="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX56="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6391,7 +6441,7 @@
         <v/>
       </c>
       <c r="BE57" s="2">
-        <f>IF($B57="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K57="Completed",$M57=""),"Completed visit missing Visit Notes",""),IF(AND($K57="Completed",$S57=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ57="Offer Sent",OR($X57="",$AA57="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ57="Active Negotiation",OR($AE57="",$AF57="",$AH57="",$AG57="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ57="Contract Sent",$AT57="",$R57=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ57="Contract Signed",$AU57=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ57="Long-Term Nurture",OR($AG57="",$AG57&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ57="Lost / Closed Out",OR($AR57="",$AS57="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM57="Sent",$AO57=""),"Gift marked Sent without recorded approval",""),IF($AX57="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B57="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K57="Completed",$M57=""),"Completed visit missing Visit Notes",""),IF(AND($K57="Completed",$S57=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ57="Offer Sent",OR($X57="",$AA57="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ57="Active Negotiation",OR($AE57="",$AF57="",$AH57="",$AG57="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ57="Contract Sent",$AT57="",$R57=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ57="Contract Signed",$AU57=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ57="Long-Term Nurture",OR($AG57="",$AG57&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ57="Lost / Closed Out",OR($AR57="",$AS57="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM57="Sent",OR($BH57="",$BI57="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX57="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6429,7 +6479,7 @@
         <v/>
       </c>
       <c r="BE58" s="2">
-        <f>IF($B58="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K58="Completed",$M58=""),"Completed visit missing Visit Notes",""),IF(AND($K58="Completed",$S58=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ58="Offer Sent",OR($X58="",$AA58="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ58="Active Negotiation",OR($AE58="",$AF58="",$AH58="",$AG58="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ58="Contract Sent",$AT58="",$R58=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ58="Contract Signed",$AU58=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ58="Long-Term Nurture",OR($AG58="",$AG58&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ58="Lost / Closed Out",OR($AR58="",$AS58="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM58="Sent",$AO58=""),"Gift marked Sent without recorded approval",""),IF($AX58="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B58="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K58="Completed",$M58=""),"Completed visit missing Visit Notes",""),IF(AND($K58="Completed",$S58=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ58="Offer Sent",OR($X58="",$AA58="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ58="Active Negotiation",OR($AE58="",$AF58="",$AH58="",$AG58="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ58="Contract Sent",$AT58="",$R58=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ58="Contract Signed",$AU58=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ58="Long-Term Nurture",OR($AG58="",$AG58&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ58="Lost / Closed Out",OR($AR58="",$AS58="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM58="Sent",OR($BH58="",$BI58="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX58="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6467,7 +6517,7 @@
         <v/>
       </c>
       <c r="BE59" s="2">
-        <f>IF($B59="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K59="Completed",$M59=""),"Completed visit missing Visit Notes",""),IF(AND($K59="Completed",$S59=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ59="Offer Sent",OR($X59="",$AA59="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ59="Active Negotiation",OR($AE59="",$AF59="",$AH59="",$AG59="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ59="Contract Sent",$AT59="",$R59=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ59="Contract Signed",$AU59=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ59="Long-Term Nurture",OR($AG59="",$AG59&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ59="Lost / Closed Out",OR($AR59="",$AS59="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM59="Sent",$AO59=""),"Gift marked Sent without recorded approval",""),IF($AX59="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B59="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K59="Completed",$M59=""),"Completed visit missing Visit Notes",""),IF(AND($K59="Completed",$S59=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ59="Offer Sent",OR($X59="",$AA59="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ59="Active Negotiation",OR($AE59="",$AF59="",$AH59="",$AG59="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ59="Contract Sent",$AT59="",$R59=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ59="Contract Signed",$AU59=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ59="Long-Term Nurture",OR($AG59="",$AG59&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ59="Lost / Closed Out",OR($AR59="",$AS59="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM59="Sent",OR($BH59="",$BI59="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX59="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
@@ -6505,12 +6555,12 @@
         <v/>
       </c>
       <c r="BE60" s="2">
-        <f>IF($B60="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K60="Completed",$M60=""),"Completed visit missing Visit Notes",""),IF(AND($K60="Completed",$S60=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ60="Offer Sent",OR($X60="",$AA60="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ60="Active Negotiation",OR($AE60="",$AF60="",$AH60="",$AG60="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ60="Contract Sent",$AT60="",$R60=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ60="Contract Signed",$AU60=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ60="Long-Term Nurture",OR($AG60="",$AG60&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ60="Lost / Closed Out",OR($AR60="",$AS60="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM60="Sent",$AO60=""),"Gift marked Sent without recorded approval",""),IF($AX60="Duplicate","Duplicate active record for this address","")))</f>
+        <f>IF($B60="","",_xlfn.TEXTJOIN(" | ",TRUE,IF(AND($K60="Completed",$M60=""),"Completed visit missing Visit Notes",""),IF(AND($K60="Completed",$S60=""),"Completed visit missing Seller Motivation (or add Exception note)",""),IF(AND($AQ60="Offer Sent",OR($X60="",$AA60="")),"Offer Sent needs Approved Offer Amount + Offer Sent Date",""),IF(AND($AQ60="Active Negotiation",OR($AE60="",$AF60="",$AH60="",$AG60="")),"Active Negotiation needs Last Contact Result + Next Action + Owner + Due Date",""),IF(AND($AQ60="Contract Sent",$AT60="",$R60=""),"Contract Sent needs Contract Sent Date or File Link",""),IF(AND($AQ60="Contract Signed",$AU60=""),"Contract Signed needs Contract Signed Date",""),IF(AND($AQ60="Long-Term Nurture",OR($AG60="",$AG60&lt;=TODAY())),"Long-Term Nurture needs an exact FUTURE follow-up date",""),IF(AND($AQ60="Lost / Closed Out",OR($AR60="",$AS60="")),"Lost / Closed Out needs Final Disposition + Closeout Reason",""),IF(AND($AM60="Sent",OR($BH60="",$BI60="")),"Gift marked Sent without recorded approval (needs Gift Approved By + Gift Approval Date)",""),IF($AX60="Duplicate","Duplicate active record for this address","")))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:BG60">
+  <conditionalFormatting sqref="A2:BI60">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$BD2="Exception"</formula>
     </cfRule>
@@ -6527,7 +6577,7 @@
       <formula>$AQ2="Contract Signed"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="19">
+  <dataValidations count="20">
     <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a value from the list." prompt="Allowed: Direct Mail,Direct Mail - Postcard,PPC,TV,Facebook,SEO,PPL - Property Leads,PPL - Motivated Leads" type="list">
       <formula1>"Direct Mail,Direct Mail - Postcard,PPC,TV,Facebook,SEO,PPL - Property Leads,PPL - Motivated Leads"</formula1>
     </dataValidation>
@@ -6585,6 +6635,9 @@
     <dataValidation sqref="BG2:BG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a value from the list." prompt="Allowed: Yes,No" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
+    <dataValidation sqref="BH2:BH1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Pick a value from the list." prompt="Allowed: Cherry,Juan" type="list">
+      <formula1>"Cherry,Juan"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6596,7 +6649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -6620,6 +6673,7 @@
     <col width="26" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
     <col width="26" customWidth="1" min="21" max="21"/>
+    <col width="26" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6650,80 +6704,85 @@
       </c>
       <c r="F1" s="22" t="inlineStr">
         <is>
+          <t>Gift Approved By</t>
+        </is>
+      </c>
+      <c r="G1" s="22" t="inlineStr">
+        <is>
           <t>Updated By</t>
         </is>
       </c>
-      <c r="G1" s="22" t="inlineStr">
+      <c r="H1" s="22" t="inlineStr">
         <is>
           <t>Final Disposition</t>
         </is>
       </c>
-      <c r="H1" s="22" t="inlineStr">
+      <c r="I1" s="22" t="inlineStr">
         <is>
           <t>Gift Status</t>
         </is>
       </c>
-      <c r="I1" s="22" t="inlineStr">
+      <c r="J1" s="22" t="inlineStr">
         <is>
           <t>Blocker</t>
         </is>
       </c>
-      <c r="J1" s="22" t="inlineStr">
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>Lead Source</t>
         </is>
       </c>
-      <c r="K1" s="22" t="inlineStr">
+      <c r="L1" s="22" t="inlineStr">
         <is>
           <t>Offer Status</t>
         </is>
       </c>
-      <c r="L1" s="22" t="inlineStr">
+      <c r="M1" s="22" t="inlineStr">
         <is>
           <t>Occupancy Status</t>
         </is>
       </c>
-      <c r="M1" s="22" t="inlineStr">
+      <c r="N1" s="22" t="inlineStr">
         <is>
           <t>Property Condition</t>
         </is>
       </c>
-      <c r="N1" s="22" t="inlineStr">
+      <c r="O1" s="22" t="inlineStr">
         <is>
           <t>Seller Timeline</t>
         </is>
       </c>
-      <c r="O1" s="22" t="inlineStr">
+      <c r="P1" s="22" t="inlineStr">
         <is>
           <t>Offer Received Confirmation</t>
         </is>
       </c>
-      <c r="P1" s="22" t="inlineStr">
+      <c r="Q1" s="22" t="inlineStr">
         <is>
           <t>Transaction Handoff Status</t>
         </is>
       </c>
-      <c r="Q1" s="22" t="inlineStr">
+      <c r="R1" s="22" t="inlineStr">
         <is>
           <t>REI Update Required</t>
         </is>
       </c>
-      <c r="R1" s="22" t="inlineStr">
+      <c r="S1" s="22" t="inlineStr">
         <is>
           <t>REI Update Completed</t>
         </is>
       </c>
-      <c r="S1" s="22" t="inlineStr">
+      <c r="T1" s="22" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="T1" s="22" t="inlineStr">
+      <c r="U1" s="22" t="inlineStr">
         <is>
           <t>Data Quality Status</t>
         </is>
       </c>
-      <c r="U1" s="22" t="inlineStr">
+      <c r="V1" s="22" t="inlineStr">
         <is>
           <t>Stalled Status</t>
         </is>
@@ -6757,80 +6816,85 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
+          <t>Cherry</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>Jonathan</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Contracted</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Not Reviewed</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Price</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Direct Mail</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Not Started</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Owner-Occupied</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Excellent</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>ASAP</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Not Ready</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Manual</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6864,80 +6928,85 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>Juan</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Kyle</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Lost</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Direct Mail - Postcard</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>In Preparation</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Tenant-Occupied</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Good</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
         <is>
           <t>30 days</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="Q3" s="2" t="inlineStr">
         <is>
           <t>Ready for Handoff</t>
         </is>
       </c>
-      <c r="Q3" s="2" t="inlineStr">
+      <c r="R3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>Apps Script</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -6964,62 +7033,62 @@
           <t>Cherry</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cherry</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Long-Term Nurture</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>Tenant</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>PPC</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Sent</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Vacant</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Fair</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>60 days</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>Handed Off to JM</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Exception</t>
         </is>
@@ -7046,57 +7115,57 @@
           <t>Jonathan</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Juan</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Closed Out</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Sent</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>Family</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>TV</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Countered</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>90+ days</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>JM Confirmed</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>TEST</t>
         </is>
@@ -7118,37 +7187,37 @@
           <t>JM</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>JM</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>Not Appropriate</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>Access</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Accepted</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Distressed</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -7165,22 +7234,22 @@
           <t>Cesar</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Apps Script</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>Timing</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>SEO</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Rejected</t>
         </is>
@@ -7197,22 +7266,22 @@
           <t>Jose Herrera</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Import</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>Documents</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>PPL - Property Leads</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Withdrawn</t>
         </is>
@@ -7229,12 +7298,12 @@
           <t>Manny Morales</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="2" t="inlineStr">
         <is>
           <t>Property Condition</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>PPL - Motivated Leads</t>
         </is>
@@ -7251,7 +7320,7 @@
           <t>Lily</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>Seller Unresponsive</t>
         </is>
@@ -7268,7 +7337,7 @@
           <t>Alan Hernandez</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
